--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -14177,16 +14177,16 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="O86" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.02060285195024946</v>
+        <v>0.0332455111015389</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -16349,16 +16349,16 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="O100" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.001872986540931769</v>
+        <v>0.02294408512641417</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -18482,12 +18482,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -18521,16 +18521,16 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>0.0004682466352329422</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -18563,40 +18563,188 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
+      <c r="AT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW114" t="inlineStr">
+      <c r="AW115" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
+      <c r="AX115" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY114" t="inlineStr">
+      <c r="AY115" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
+      <c r="AZ115" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA114" t="inlineStr">
+      <c r="BA115" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB114" t="inlineStr">
+      <c r="BB115" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC114" t="inlineStr">
+      <c r="BC115" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -18718,7 +18866,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -18728,7 +18876,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
@@ -18780,7 +18928,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>515</v>
+        <v>588</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -18750,6 +18750,154 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>2</v>
+      </c>
+      <c r="O116" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18783,7 +18931,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -18866,7 +19014,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -18876,7 +19024,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -18928,7 +19076,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1454,9 +1451,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1602,9 +1596,6 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -1750,9 +1741,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -3774,9 +3762,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4167,9 +4152,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4315,9 +4297,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4463,9 +4442,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -6339,9 +6315,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="S37" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6732,9 +6705,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6880,9 +6850,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -7028,9 +6995,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8608,9 +8572,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8756,9 +8717,6 @@
       <c r="O52" t="n">
         <v>87</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.04073745726526598</v>
       </c>
@@ -8904,9 +8862,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9297,9 +9252,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9445,9 +9397,6 @@
       <c r="O56" t="n">
         <v>3</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -9593,9 +9542,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -11173,9 +11119,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -11321,9 +11264,6 @@
       <c r="O68" t="n">
         <v>69</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.03230901783107301</v>
       </c>
@@ -11469,9 +11409,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="S69" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11862,9 +11799,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -12010,9 +11944,6 @@
       <c r="O72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -12158,9 +12089,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13886,9 +13814,6 @@
       <c r="O84" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -14034,9 +13959,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -14182,9 +14104,6 @@
       <c r="O86" t="n">
         <v>71</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.0332455111015389</v>
       </c>
@@ -14330,9 +14249,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14478,9 +14394,6 @@
       <c r="O88" t="n">
         <v>4</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.007751879695168184</v>
       </c>
@@ -14626,9 +14539,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -15022,9 +14932,6 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -15170,9 +15077,6 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -15318,9 +15222,6 @@
       <c r="O93" t="n">
         <v>2</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -15466,9 +15367,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15614,9 +15512,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -15762,9 +15657,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15910,9 +15802,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -16058,9 +15947,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -16206,9 +16092,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -16354,9 +16237,6 @@
       <c r="O100" t="n">
         <v>49</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.02294408512641417</v>
       </c>
@@ -16502,9 +16382,6 @@
       <c r="O101" t="n">
         <v>1</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -16650,9 +16527,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -17046,9 +16920,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -17194,9 +17065,6 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -17342,9 +17210,6 @@
       <c r="O106" t="n">
         <v>4</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.003267233630263065</v>
       </c>
@@ -17490,9 +17355,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -17638,9 +17500,6 @@
       <c r="O108" t="n">
         <v>2</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -17786,9 +17645,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17934,9 +17790,6 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -18082,9 +17935,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -18230,9 +18080,6 @@
       <c r="O112" t="n">
         <v>2</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -18378,9 +18225,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -18526,9 +18370,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.0004682466352329422</v>
       </c>
@@ -18674,9 +18515,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18821,9 +18659,6 @@
       </c>
       <c r="O116" t="n">
         <v>2</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0.001633616815131532</v>

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -14205,12 +14205,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -14244,81 +14244,92 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TETANUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TETANUS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14345,17 +14356,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -14389,81 +14400,170 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>4</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0.007751879695168184</v>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TETANUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TETANUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary tetanus notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN88" t="b">
+        <v>1</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_TETANUS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14495,12 +14595,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -14547,82 +14647,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14649,17 +14735,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -14693,170 +14779,81 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Stelkramp</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN90" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.007751879695168184</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14885,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -14918,7 +14915,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -14927,81 +14924,95 @@
         </is>
       </c>
       <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT91" t="n">
         <v>1</v>
       </c>
-      <c r="O91" t="n">
-        <v>1</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP91" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
-      <c r="AT91" t="n">
-        <v>0</v>
-      </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15028,17 +15039,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -15063,7 +15074,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -15072,81 +15083,170 @@
         </is>
       </c>
       <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Stelkramp</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
         <v>1</v>
       </c>
-      <c r="O92" t="n">
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT92" t="n">
         <v>1</v>
       </c>
-      <c r="R92" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP92" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
-      <c r="AT92" t="n">
-        <v>0</v>
-      </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15208,7 +15308,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -15217,13 +15317,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R93" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -15353,7 +15453,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -15362,13 +15462,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -15498,7 +15598,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -15507,13 +15607,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -15643,7 +15743,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -15788,7 +15888,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -15797,13 +15897,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -15933,7 +16033,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -16048,12 +16148,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -16078,12 +16178,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -16126,42 +16226,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16193,12 +16293,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -16223,22 +16323,22 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.02294408512641417</v>
+        <v>0</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -16271,42 +16371,42 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16338,12 +16438,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -16377,13 +16477,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -16416,42 +16516,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16483,12 +16583,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -16522,95 +16622,81 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="R102" t="n">
-        <v>0.009344880428283346</v>
+        <v>0.02294408512641417</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -16637,17 +16723,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -16686,165 +16772,76 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>Stelkramp</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE103" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF103" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG103" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN103" t="b">
-        <v>1</v>
+      <c r="R103" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16876,12 +16873,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -16906,7 +16903,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -16915,81 +16912,95 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17016,17 +17027,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -17051,7 +17062,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -17065,76 +17076,165 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
-      <c r="R105" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Stelkramp</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17296,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -17205,13 +17305,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0.003267233630263065</v>
+        <v>0</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -17341,7 +17441,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -17350,13 +17450,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -17486,7 +17586,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -17495,13 +17595,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R108" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -17631,7 +17731,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -17776,7 +17876,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -17785,13 +17885,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R110" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -17921,7 +18021,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -18066,7 +18166,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -18075,13 +18175,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -18181,12 +18281,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -18211,12 +18311,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N113" t="n">
@@ -18259,42 +18359,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18326,12 +18426,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -18356,22 +18456,22 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R114" t="n">
-        <v>0.0004682466352329422</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -18404,42 +18504,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18471,12 +18571,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -18549,42 +18649,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18616,12 +18716,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -18646,7 +18746,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -18655,13 +18755,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0004682466352329422</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -18694,40 +18794,330 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>2</v>
+      </c>
+      <c r="O118" t="n">
+        <v>2</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW116" t="inlineStr">
+      <c r="AW118" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
+      <c r="AX118" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY116" t="inlineStr">
+      <c r="AY118" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
+      <c r="AZ118" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA116" t="inlineStr">
+      <c r="BA118" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB116" t="inlineStr">
+      <c r="BB118" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC116" t="inlineStr">
+      <c r="BC118" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18849,7 +19239,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -18859,7 +19249,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -18879,7 +19269,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -18911,7 +19301,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -19123,6 +19123,151 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19156,7 +19301,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -19239,7 +19384,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -19249,7 +19394,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
@@ -19301,7 +19446,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -19268,6 +19268,151 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19301,7 +19446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19384,7 +19529,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -19394,7 +19539,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -26972,12 +26972,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -27011,13 +27011,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -27050,42 +27050,42 @@
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27117,12 +27117,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -27162,89 +27162,75 @@
         <v>1</v>
       </c>
       <c r="R156" t="n">
-        <v>0.009344880428283346</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27271,7 +27257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -27320,98 +27306,23 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
+      <c r="R157" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TETANUS</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Stelkramp</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN157" t="b">
-        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
@@ -27505,17 +27416,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27540,7 +27451,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -27549,81 +27460,170 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Stelkramp</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN158" t="b">
+        <v>1</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TETANUS</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27655,12 +27655,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27694,13 +27694,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27733,42 +27733,42 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27800,12 +27800,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -27839,93 +27839,81 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O160" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27952,7 +27940,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -28004,98 +27992,18 @@
       <c r="P161" t="n">
         <v>0</v>
       </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE161" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN161" t="b">
-        <v>1</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -28189,17 +28097,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -28224,7 +28132,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -28233,81 +28141,173 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>4</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28339,12 +28339,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -28378,13 +28378,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O163" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -28417,42 +28417,42 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28484,12 +28484,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -28528,9 +28528,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="P164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -28539,77 +28536,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28636,7 +28624,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -28688,98 +28676,18 @@
       <c r="P165" t="n">
         <v>0</v>
       </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
-        <v>1</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
@@ -28873,17 +28781,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28908,7 +28816,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -28917,81 +28825,173 @@
         </is>
       </c>
       <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN166" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
         <v>2</v>
       </c>
-      <c r="O166" t="n">
-        <v>2</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP166" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
-      <c r="AT166" t="n">
-        <v>0</v>
-      </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29023,12 +29023,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -29062,13 +29062,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -29101,42 +29101,42 @@
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29168,12 +29168,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -29212,9 +29212,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -29223,77 +29220,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29320,7 +29308,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -29372,98 +29360,18 @@
       <c r="P169" t="n">
         <v>0</v>
       </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE169" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF169" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG169" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN169" t="b">
-        <v>1</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
@@ -29557,17 +29465,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -29592,7 +29500,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -29601,81 +29509,173 @@
         </is>
       </c>
       <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
         <v>1</v>
       </c>
-      <c r="O170" t="n">
-        <v>1</v>
-      </c>
-      <c r="R170" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29707,12 +29707,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -29746,13 +29746,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -29785,42 +29785,42 @@
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29852,12 +29852,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -29882,7 +29882,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -29891,13 +29891,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>0.001633616815131532</v>
+        <v>0</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -29930,42 +29930,42 @@
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29997,12 +29997,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -30036,93 +30036,81 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O173" t="n">
-        <v>0</v>
-      </c>
-      <c r="P173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30137,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -30201,98 +30189,18 @@
       <c r="P174" t="n">
         <v>0</v>
       </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE174" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF174" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG174" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN174" t="b">
-        <v>1</v>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
@@ -30386,17 +30294,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -30421,12 +30329,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N175" t="n">
@@ -30435,76 +30343,168 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="R175" t="n">
-        <v>0</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>1</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30536,12 +30536,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -30575,13 +30575,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>0.0004682466352329422</v>
+        <v>0</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -30614,42 +30614,42 @@
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30681,12 +30681,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -30720,13 +30720,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>0.0004682466352329422</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -30759,42 +30759,42 @@
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -30826,12 +30826,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -30856,7 +30856,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -30865,13 +30865,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>0.001633616815131532</v>
+        <v>0</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -30904,42 +30904,42 @@
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -30971,12 +30971,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -31010,93 +31010,81 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O179" t="n">
-        <v>0</v>
-      </c>
-      <c r="P179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31123,7 +31111,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -31175,98 +31163,18 @@
       <c r="P180" t="n">
         <v>0</v>
       </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X180" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R180" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE180" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF180" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG180" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN180" t="b">
-        <v>1</v>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
@@ -31360,17 +31268,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -31395,7 +31303,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -31404,81 +31312,173 @@
         </is>
       </c>
       <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN181" t="b">
         <v>1</v>
       </c>
-      <c r="O181" t="n">
-        <v>1</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -31510,12 +31510,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -31549,93 +31549,81 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31662,7 +31650,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -31714,98 +31702,18 @@
       <c r="P183" t="n">
         <v>0</v>
       </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -31899,17 +31807,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -31934,7 +31842,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -31948,76 +31856,168 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="R184" t="n">
-        <v>0</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
+        <v>1</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32049,12 +32049,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -32093,9 +32093,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="P185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -32104,77 +32101,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32201,7 +32189,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -32253,98 +32241,18 @@
       <c r="P186" t="n">
         <v>0</v>
       </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TETANUS</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN186" t="b">
-        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
@@ -32410,6 +32318,243 @@
         </is>
       </c>
       <c r="BC186" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN187" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TETANUS; SER_SG_HIST_TETANUS</t>
+        </is>
+      </c>
+      <c r="AT187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV187" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA187" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC187" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -32531,7 +32676,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
@@ -32541,7 +32686,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d120/2026-2029.xlsx
+++ b/diseases/d120/2026-2029.xlsx
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1774,17 +1774,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2000,7 +2005,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2008,17 +2013,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -6043,7 +6053,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6051,17 +6061,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6277,7 +6292,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -6285,17 +6300,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -10172,7 +10192,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -10180,17 +10200,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -10406,7 +10431,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -10414,17 +10439,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -14689,7 +14719,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -14697,17 +14727,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -14923,7 +14958,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -14931,17 +14966,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -18812,7 +18852,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -18820,17 +18860,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -19046,7 +19091,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
@@ -19054,17 +19099,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS108" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -23622,7 +23672,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
@@ -23630,17 +23680,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS135" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -23856,7 +23911,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
@@ -23864,17 +23919,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS136" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -26866,13 +26926,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="O154" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="R154" t="n">
-        <v>0.02294408512641417</v>
+        <v>0.03277726446630596</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -27331,7 +27391,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
@@ -27339,17 +27399,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS157" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -27565,7 +27630,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
@@ -27573,17 +27638,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS158" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TETANUS</t>
         </is>
       </c>
       <c r="AT158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -30720,13 +30790,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O177" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R177" t="n">
-        <v>0.0004682466352329422</v>
+        <v>0.004214219717096481</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -32738,7 +32808,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>592</v>
+        <v>621</v>
       </c>
     </row>
     <row r="16">
